--- a/_ForDRA/BVSimulationFiles/92.xlsx
+++ b/_ForDRA/BVSimulationFiles/92.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0004725274725274725</v>
+        <v>0.009450549450549449</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004903639283782444</v>
+        <v>0.009807278567564887</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005080613700043555</v>
+        <v>0.01016122740008711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005256205839973419</v>
+        <v>0.01051241167994684</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000543042353023373</v>
+        <v>0.01086084706046746</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005603274558415614</v>
+        <v>0.01120654911683123</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000577476667322187</v>
+        <v>0.01154953334644374</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0005944907584648429</v>
+        <v>0.01188981516929686</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0006113704964164982</v>
+        <v>0.01222740992832996</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006281166444894807</v>
+        <v>0.01256233288978961</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006447299621793793</v>
+        <v>0.01289459924358759</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0006612112051828657</v>
+        <v>0.01322422410365731</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0006775611254154375</v>
+        <v>0.01355122250830875</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0006937804710290807</v>
+        <v>0.01387560942058161</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007098699864298533</v>
+        <v>0.01419739972859707</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007258304122953915</v>
+        <v>0.01451660824590783</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007416624855923356</v>
+        <v>0.01483324971184671</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007573669395936799</v>
+        <v>0.0151473387918736</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007729445038960422</v>
+        <v>0.01545889007792084</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0007883959044368599</v>
+        <v>0.0157679180887372</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0004725274725274725</v>
+        <v>0.009450549450549449</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004903639283782444</v>
+        <v>0.009807278567564887</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005080613700043555</v>
+        <v>0.01016122740008711</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005256205839973419</v>
+        <v>0.01051241167994684</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000543042353023373</v>
+        <v>0.01086084706046746</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005603274558415614</v>
+        <v>0.01120654911683123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000577476667322187</v>
+        <v>0.01154953334644374</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005944907584648429</v>
+        <v>0.01188981516929686</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006113704964164982</v>
+        <v>0.01222740992832996</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006281166444894807</v>
+        <v>0.01256233288978961</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006447299621793793</v>
+        <v>0.01289459924358759</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006612112051828657</v>
+        <v>0.01322422410365731</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0006775611254154375</v>
+        <v>0.01355122250830875</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0006937804710290807</v>
+        <v>0.01387560942058161</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007098699864298533</v>
+        <v>0.01419739972859707</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0007258304122953915</v>
+        <v>0.01451660824590783</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007416624855923356</v>
+        <v>0.01483324971184671</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007573669395936799</v>
+        <v>0.0151473387918736</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007729445038960422</v>
+        <v>0.01545889007792084</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0007883959044368599</v>
+        <v>0.0157679180887372</v>
       </c>
     </row>
   </sheetData>
